--- a/site/ServiceNow-Entra-ID-Okta-Integration-Guide/headings.xlsx
+++ b/site/ServiceNow-Entra-ID-Okta-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -705,7 +705,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Unique Identity</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -727,7 +727,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Password Policy</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,19 +737,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>h_01KJYAJA8C7S34KTD95WP3VDWF</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYAJA8C7S34KTD95WP3VDWF</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Notifications Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,63 +759,63 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>h_01KJYAJA8CKVJMV2D2NG3MTMPJ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYAJA8CKVJMV2D2NG3MTMPJ</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01K9750G1WVCA080W3BF2A4RY4</t>
+          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01K9750G1WVCA080W3BF2A4RY4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Onboarding Notification Settings</t>
+          <t>Notifications Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KJY7CCJQ8PXYADMFEDT4V3CW</t>
+          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJY7CCJQ8PXYADMFEDT4V3CW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Offboarding Notification Settings</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,85 +825,85 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KJY7CCJQ81FCYKPN3FSGM28D</t>
+          <t>h_01K9750G1WVCA080W3BF2A4RY4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJY7CCJQ81FCYKPN3FSGM28D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01K9750G1WVCA080W3BF2A4RY4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Onboarding Notification Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>h_01KJYAJA8CW38M9AND8VAX3839</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYAJA8CW38M9AND8VAX3839</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Offboarding Notification Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
+          <t>h_01KJYAJA8CR4AP19V87XS8KG1C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYAJA8CR4AP19V87XS8KG1C</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Group Rules</t>
+          <t>Log Insight Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>01JVC7QW1983644JGH2WGK8FWX</t>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01JVC7QW1983644JGH2WGK8FWX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,54 +913,98 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
+          <t>h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Group Rules</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>01JVC7QW1983644JGH2WGK8FWX</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01JVC7QW1983644JGH2WGK8FWX</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/ServiceNow-Entra-ID-Okta-Integration-Guide/headings.xlsx
+++ b/site/ServiceNow-Entra-ID-Okta-Integration-Guide/headings.xlsx
@@ -737,12 +737,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KJYAJA8C7S34KTD95WP3VDWF</t>
+          <t>h_01KJYCFGY00P3DCSPHSZ72MP8V</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYAJA8C7S34KTD95WP3VDWF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY00P3DCSPHSZ72MP8V</t>
         </is>
       </c>
     </row>
@@ -759,12 +759,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KJYAJA8CKVJMV2D2NG3MTMPJ</t>
+          <t>h_01KJYCFGY05MHFN0SZFPMHCY8Q</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYAJA8CKVJMV2D2NG3MTMPJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY05MHFN0SZFPMHCY8Q</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KJYAJA8CW38M9AND8VAX3839</t>
+          <t>h_01KJYCFGY0AG0E1C2SFT0ZEDDK</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYAJA8CW38M9AND8VAX3839</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY0AG0E1C2SFT0ZEDDK</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KJYAJA8CR4AP19V87XS8KG1C</t>
+          <t>h_01KJYCFGY02MABCNX128SC7YSA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYAJA8CR4AP19V87XS8KG1C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY02MABCNX128SC7YSA</t>
         </is>
       </c>
     </row>

--- a/site/ServiceNow-Entra-ID-Okta-Integration-Guide/headings.xlsx
+++ b/site/ServiceNow-Entra-ID-Okta-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,29 +683,29 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Offboarding</t>
+          <t>Create Contractor Settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KGPAMEAWJDEJ5ZJJRVVJHBR8</t>
+          <t>h_01KJYVN85SXZD8FN96TD2FKN3K</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KGPAMEAWJDEJ5ZJJRVVJHBR8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYVN85SXZD8FN96TD2FKN3K</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unique Identity</t>
+          <t>Offboarding</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,19 +715,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
+          <t>h_01KGPAMEAWJDEJ5ZJJRVVJHBR8</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KGPAMEAWJDEJ5ZJJRVVJHBR8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Password Policy</t>
+          <t>Unique Identity</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,19 +737,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KJYCFGY00P3DCSPHSZ72MP8V</t>
+          <t>h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY00P3DCSPHSZ72MP8V</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Password Policy</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,19 +759,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KJYCFGY05MHFN0SZFPMHCY8Q</t>
+          <t>h_01KJYCFGY00P3DCSPHSZ72MP8V</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY05MHFN0SZFPMHCY8Q</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY00P3DCSPHSZ72MP8V</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,19 +781,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>h_01KJYCFGY05MHFN0SZFPMHCY8Q</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY05MHFN0SZFPMHCY8Q</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Notifications Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,41 +803,41 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Notifications Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01K9750G1WVCA080W3BF2A4RY4</t>
+          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01K9750G1WVCA080W3BF2A4RY4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Onboarding Notification Settings</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,19 +847,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KJYCFGY0AG0E1C2SFT0ZEDDK</t>
+          <t>h_01K9750G1WVCA080W3BF2A4RY4</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY0AG0E1C2SFT0ZEDDK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01K9750G1WVCA080W3BF2A4RY4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Offboarding Notification Settings</t>
+          <t>Onboarding Notification Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,63 +869,63 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KJYCFGY02MABCNX128SC7YSA</t>
+          <t>h_01KJYCFGY0AG0E1C2SFT0ZEDDK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY02MABCNX128SC7YSA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY0AG0E1C2SFT0ZEDDK</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Offboarding Notification Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>h_01KJYCFGY02MABCNX128SC7YSA</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY02MABCNX128SC7YSA</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Log Insight Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Group Rules</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,19 +935,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>01JVC7QW1983644JGH2WGK8FWX</t>
+          <t>h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01JVC7QW1983644JGH2WGK8FWX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Group Rules</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,54 +957,76 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
+          <t>01JVC7QW1983644JGH2WGK8FWX</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01JVC7QW1983644JGH2WGK8FWX</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/ServiceNow-Entra-ID-Okta-Integration-Guide/headings.xlsx
+++ b/site/ServiceNow-Entra-ID-Okta-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -727,29 +727,29 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unique Identity</t>
+          <t>Terminate Contractor Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
+          <t>h_01KK10NCCN95NYPDR3N3EM30PC</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KK10NCCN95NYPDR3N3EM30PC</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Password Policy</t>
+          <t>Unique Identity</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,19 +759,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KJYCFGY00P3DCSPHSZ72MP8V</t>
+          <t>h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY00P3DCSPHSZ72MP8V</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Password Policy</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,19 +781,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KJYCFGY05MHFN0SZFPMHCY8Q</t>
+          <t>h_01KJYCFGY00P3DCSPHSZ72MP8V</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY05MHFN0SZFPMHCY8Q</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY00P3DCSPHSZ72MP8V</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>h_01KJYCFGY05MHFN0SZFPMHCY8Q</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY05MHFN0SZFPMHCY8Q</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Notifications Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,41 +825,41 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Notifications Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01K9750G1WVCA080W3BF2A4RY4</t>
+          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01K9750G1WVCA080W3BF2A4RY4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Onboarding Notification Settings</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KJYCFGY0AG0E1C2SFT0ZEDDK</t>
+          <t>h_01K9750G1WVCA080W3BF2A4RY4</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY0AG0E1C2SFT0ZEDDK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01K9750G1WVCA080W3BF2A4RY4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Offboarding Notification Settings</t>
+          <t>Onboarding Notification Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,63 +891,63 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KJYCFGY02MABCNX128SC7YSA</t>
+          <t>h_01KJYCFGY0AG0E1C2SFT0ZEDDK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY02MABCNX128SC7YSA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY0AG0E1C2SFT0ZEDDK</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Offboarding Notification Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>h_01KJYCFGY02MABCNX128SC7YSA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY02MABCNX128SC7YSA</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Log Insight Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Group Rules</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,19 +957,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>01JVC7QW1983644JGH2WGK8FWX</t>
+          <t>h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01JVC7QW1983644JGH2WGK8FWX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Group Rules</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,54 +979,76 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
+          <t>01JVC7QW1983644JGH2WGK8FWX</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01JVC7QW1983644JGH2WGK8FWX</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/ServiceNow-Entra-ID-Okta-Integration-Guide/headings.xlsx
+++ b/site/ServiceNow-Entra-ID-Okta-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -727,7 +727,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Terminate Contractor Settings</t>
+          <t>Correlation Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,41 +737,41 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KK10NCCN95NYPDR3N3EM30PC</t>
+          <t>h_01KK15VCERBY2EME9DV8NT84PA</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KK10NCCN95NYPDR3N3EM30PC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KK15VCERBY2EME9DV8NT84PA</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unique Identity</t>
+          <t>Terminate Contractor Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
+          <t>h_01KK15VCER2A72S88FKQCSX5AG</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KK15VCER2A72S88FKQCSX5AG</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Password Policy</t>
+          <t>Unique Identity</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,19 +781,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KJYCFGY00P3DCSPHSZ72MP8V</t>
+          <t>h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY00P3DCSPHSZ72MP8V</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Password Policy</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KJYCFGY05MHFN0SZFPMHCY8Q</t>
+          <t>h_01KJYCFGY00P3DCSPHSZ72MP8V</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY05MHFN0SZFPMHCY8Q</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY00P3DCSPHSZ72MP8V</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,19 +825,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>h_01KJYCFGY05MHFN0SZFPMHCY8Q</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY05MHFN0SZFPMHCY8Q</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Notifications Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,41 +847,41 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Notifications Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01K9750G1WVCA080W3BF2A4RY4</t>
+          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01K9750G1WVCA080W3BF2A4RY4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Onboarding Notification Settings</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,19 +891,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KJYCFGY0AG0E1C2SFT0ZEDDK</t>
+          <t>h_01K9750G1WVCA080W3BF2A4RY4</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY0AG0E1C2SFT0ZEDDK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01K9750G1WVCA080W3BF2A4RY4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Offboarding Notification Settings</t>
+          <t>Onboarding Notification Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,63 +913,63 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KJYCFGY02MABCNX128SC7YSA</t>
+          <t>h_01KJYCFGY0AG0E1C2SFT0ZEDDK</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY02MABCNX128SC7YSA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY0AG0E1C2SFT0ZEDDK</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Offboarding Notification Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>h_01KJYCFGY02MABCNX128SC7YSA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY02MABCNX128SC7YSA</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Log Insight Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Group Rules</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,19 +979,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>01JVC7QW1983644JGH2WGK8FWX</t>
+          <t>h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01JVC7QW1983644JGH2WGK8FWX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Group Rules</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1001,54 +1001,76 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
+          <t>01JVC7QW1983644JGH2WGK8FWX</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01JVC7QW1983644JGH2WGK8FWX</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/ServiceNow-Entra-ID-Okta-Integration-Guide/headings.xlsx
+++ b/site/ServiceNow-Entra-ID-Okta-Integration-Guide/headings.xlsx
@@ -737,12 +737,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KK15VCERBY2EME9DV8NT84PA</t>
+          <t>h_01KK182AMJPTJG6CM917K3CHBJ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KK15VCERBY2EME9DV8NT84PA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KK182AMJPTJG6CM917K3CHBJ</t>
         </is>
       </c>
     </row>
@@ -759,12 +759,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KK15VCER2A72S88FKQCSX5AG</t>
+          <t>h_01KK182AMJG6XZTPQTR4CXAH6W</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KK15VCER2A72S88FKQCSX5AG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KK182AMJG6XZTPQTR4CXAH6W</t>
         </is>
       </c>
     </row>

--- a/site/ServiceNow-Entra-ID-Okta-Integration-Guide/headings.xlsx
+++ b/site/ServiceNow-Entra-ID-Okta-Integration-Guide/headings.xlsx
@@ -737,12 +737,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KK182AMJPTJG6CM917K3CHBJ</t>
+          <t>h_01KK1DNHMWVMDA9N0BPWY4SXCR</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KK182AMJPTJG6CM917K3CHBJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KK1DNHMWVMDA9N0BPWY4SXCR</t>
         </is>
       </c>
     </row>
@@ -759,12 +759,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KK182AMJG6XZTPQTR4CXAH6W</t>
+          <t>h_01KK1DNHMWH22XETP42FCKZ2RY</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KK182AMJG6XZTPQTR4CXAH6W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KK1DNHMWH22XETP42FCKZ2RY</t>
         </is>
       </c>
     </row>

--- a/site/ServiceNow-Entra-ID-Okta-Integration-Guide/headings.xlsx
+++ b/site/ServiceNow-Entra-ID-Okta-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -705,7 +705,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Offboarding</t>
+          <t>Password Policy</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,34 +715,34 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KGPAMEAWJDEJ5ZJJRVVJHBR8</t>
+          <t>h_01KJYCFGY00P3DCSPHSZ72MP8V</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KGPAMEAWJDEJ5ZJJRVVJHBR8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY00P3DCSPHSZ72MP8V</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Correlation Settings</t>
+          <t>Offboarding</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KK1DNHMWVMDA9N0BPWY4SXCR</t>
+          <t>h_01KGPAMEAWJDEJ5ZJJRVVJHBR8</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KK1DNHMWVMDA9N0BPWY4SXCR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KGPAMEAWJDEJ5ZJJRVVJHBR8</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Password Policy</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KJYCFGY00P3DCSPHSZ72MP8V</t>
+          <t>h_01KJYCFGY05MHFN0SZFPMHCY8Q</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY00P3DCSPHSZ72MP8V</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY05MHFN0SZFPMHCY8Q</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,19 +825,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KJYCFGY05MHFN0SZFPMHCY8Q</t>
+          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY05MHFN0SZFPMHCY8Q</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Notifications Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,41 +847,41 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Notifications Settings</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>h_01K9750G1WVCA080W3BF2A4RY4</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01K9750G1WVCA080W3BF2A4RY4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Onboarding Notification Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,19 +891,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01K9750G1WVCA080W3BF2A4RY4</t>
+          <t>h_01KJYCFGY0AG0E1C2SFT0ZEDDK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01K9750G1WVCA080W3BF2A4RY4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY0AG0E1C2SFT0ZEDDK</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Onboarding Notification Settings</t>
+          <t>Offboarding Notification Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,63 +913,63 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KJYCFGY0AG0E1C2SFT0ZEDDK</t>
+          <t>h_01KJYCFGY02MABCNX128SC7YSA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY0AG0E1C2SFT0ZEDDK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY02MABCNX128SC7YSA</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Offboarding Notification Settings</t>
+          <t>Log Insight Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KJYCFGY02MABCNX128SC7YSA</t>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY02MABCNX128SC7YSA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Group Rules</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,19 +979,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
+          <t>01JVC7QW1983644JGH2WGK8FWX</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01JVC7QW1983644JGH2WGK8FWX</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Group Rules</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1001,41 +1001,41 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>01JVC7QW1983644JGH2WGK8FWX</t>
+          <t>01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01JVC7QW1983644JGH2WGK8FWX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1045,32 +1045,10 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Additional Options</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/ServiceNow-Entra-ID-Okta-Integration-Guide/headings.xlsx
+++ b/site/ServiceNow-Entra-ID-Okta-Integration-Guide/headings.xlsx
@@ -705,7 +705,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Password Policy</t>
+          <t>Unique Identity</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,19 +715,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KJYCFGY00P3DCSPHSZ72MP8V</t>
+          <t>h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY00P3DCSPHSZ72MP8V</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Offboarding</t>
+          <t>Password Policy</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,56 +737,56 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KGPAMEAWJDEJ5ZJJRVVJHBR8</t>
+          <t>h_01KJYCFGY00P3DCSPHSZ72MP8V</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KGPAMEAWJDEJ5ZJJRVVJHBR8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY00P3DCSPHSZ72MP8V</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Terminate Contractor Settings</t>
+          <t>Offboarding</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KK1DNHMWH22XETP42FCKZ2RY</t>
+          <t>h_01KGPAMEAWJDEJ5ZJJRVVJHBR8</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KK1DNHMWH22XETP42FCKZ2RY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KGPAMEAWJDEJ5ZJJRVVJHBR8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unique Identity</t>
+          <t>Terminate Contractor Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
+          <t>h_01KK1DNHMWH22XETP42FCKZ2RY</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KK1DNHMWH22XETP42FCKZ2RY</t>
         </is>
       </c>
     </row>

--- a/site/ServiceNow-Entra-ID-Okta-Integration-Guide/headings.xlsx
+++ b/site/ServiceNow-Entra-ID-Okta-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -727,29 +727,29 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Password Policy</t>
+          <t>Unique Identity Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KJYCFGY00P3DCSPHSZ72MP8V</t>
+          <t>h_01KKBBBATHBH95WR8N2TT52EJ6</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY00P3DCSPHSZ72MP8V</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KKBBBATHBH95WR8N2TT52EJ6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Offboarding</t>
+          <t>Password Policy</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,19 +759,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KGPAMEAWJDEJ5ZJJRVVJHBR8</t>
+          <t>h_01KJYCFGY00P3DCSPHSZ72MP8V</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KGPAMEAWJDEJ5ZJJRVVJHBR8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY00P3DCSPHSZ72MP8V</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Terminate Contractor Settings</t>
+          <t>Password Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,19 +781,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KK1DNHMWH22XETP42FCKZ2RY</t>
+          <t>h_01KKBBBATH379J50NXMNECVT02</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KK1DNHMWH22XETP42FCKZ2RY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KKBBBATH379J50NXMNECVT02</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Offboarding</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,41 +803,41 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KJYCFGY05MHFN0SZFPMHCY8Q</t>
+          <t>h_01KGPAMEAWJDEJ5ZJJRVVJHBR8</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY05MHFN0SZFPMHCY8Q</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KGPAMEAWJDEJ5ZJJRVVJHBR8</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Terminate Contractor Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>h_01KK1DNHMWH22XETP42FCKZ2RY</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KK1DNHMWH22XETP42FCKZ2RY</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Notifications Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,63 +847,63 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>h_01KJYCFGY05MHFN0SZFPMHCY8Q</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY05MHFN0SZFPMHCY8Q</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01K9750G1WVCA080W3BF2A4RY4</t>
+          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01K9750G1WVCA080W3BF2A4RY4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Onboarding Notification Settings</t>
+          <t>Notifications Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KJYCFGY0AG0E1C2SFT0ZEDDK</t>
+          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY0AG0E1C2SFT0ZEDDK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Offboarding Notification Settings</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,85 +913,85 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KJYCFGY02MABCNX128SC7YSA</t>
+          <t>h_01K9750G1WVCA080W3BF2A4RY4</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY02MABCNX128SC7YSA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01K9750G1WVCA080W3BF2A4RY4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Onboarding Notification Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>h_01KJYCFGY0AG0E1C2SFT0ZEDDK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY0AG0E1C2SFT0ZEDDK</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Offboarding Notification Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
+          <t>h_01KJYCFGY02MABCNX128SC7YSA</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY02MABCNX128SC7YSA</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Group Rules</t>
+          <t>Log Insight Settings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>01JVC7QW1983644JGH2WGK8FWX</t>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01JVC7QW1983644JGH2WGK8FWX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1001,54 +1001,98 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
+          <t>h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Group Rules</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>01JVC7QW1983644JGH2WGK8FWX</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01JVC7QW1983644JGH2WGK8FWX</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/ServiceNow-Entra-ID-Okta-Integration-Guide/headings.xlsx
+++ b/site/ServiceNow-Entra-ID-Okta-Integration-Guide/headings.xlsx
@@ -737,12 +737,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KKBBBATHBH95WR8N2TT52EJ6</t>
+          <t>h_01KKBN5W79VGJ9JG0FGSVGT1A7</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KKBBBATHBH95WR8N2TT52EJ6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KKBN5W79VGJ9JG0FGSVGT1A7</t>
         </is>
       </c>
     </row>
@@ -781,12 +781,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KKBBBATH379J50NXMNECVT02</t>
+          <t>h_01KKBN5W79A97TWK76DQW39BVF</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KKBBBATH379J50NXMNECVT02</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KKBN5W79A97TWK76DQW39BVF</t>
         </is>
       </c>
     </row>

--- a/site/ServiceNow-Entra-ID-Okta-Integration-Guide/headings.xlsx
+++ b/site/ServiceNow-Entra-ID-Okta-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -837,7 +837,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Group Management</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,19 +847,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KJYCFGY05MHFN0SZFPMHCY8Q</t>
+          <t>h_01KKG6X6HY76EX8APZVS56GX9E</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY05MHFN0SZFPMHCY8Q</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KKG6X6HY76EX8APZVS56GX9E</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Sensitive Fields</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>h_01KKG6X6HYVES31WPMYGVGPPNB</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KKG6X6HYVES31WPMYGVGPPNB</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Notifications Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,63 +891,63 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>h_01KJYCFGY05MHFN0SZFPMHCY8Q</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY05MHFN0SZFPMHCY8Q</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01K9750G1WVCA080W3BF2A4RY4</t>
+          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01K9750G1WVCA080W3BF2A4RY4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Onboarding Notification Settings</t>
+          <t>Notifications Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KJYCFGY0AG0E1C2SFT0ZEDDK</t>
+          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY0AG0E1C2SFT0ZEDDK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Offboarding Notification Settings</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,85 +957,85 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KJYCFGY02MABCNX128SC7YSA</t>
+          <t>h_01K9750G1WVCA080W3BF2A4RY4</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY02MABCNX128SC7YSA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01K9750G1WVCA080W3BF2A4RY4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Onboarding Notification Settings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>h_01KJYCFGY0AG0E1C2SFT0ZEDDK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY0AG0E1C2SFT0ZEDDK</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Offboarding Notification Settings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
+          <t>h_01KJYCFGY02MABCNX128SC7YSA</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY02MABCNX128SC7YSA</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Group Rules</t>
+          <t>Log Insight Settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>01JVC7QW1983644JGH2WGK8FWX</t>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01JVC7QW1983644JGH2WGK8FWX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1045,54 +1045,98 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
+          <t>h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Group Rules</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>01JVC7QW1983644JGH2WGK8FWX</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01JVC7QW1983644JGH2WGK8FWX</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/ServiceNow-Entra-ID-Okta-Integration-Guide/headings.xlsx
+++ b/site/ServiceNow-Entra-ID-Okta-Integration-Guide/headings.xlsx
@@ -847,12 +847,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KKG6X6HY76EX8APZVS56GX9E</t>
+          <t>h_01KKGR0E1X4WS9VGW91EW6JMB7</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KKG6X6HY76EX8APZVS56GX9E</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KKGR0E1X4WS9VGW91EW6JMB7</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KKG6X6HYVES31WPMYGVGPPNB</t>
+          <t>h_01KKGR0E1X2J8YA1DX900C9W7D</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KKG6X6HYVES31WPMYGVGPPNB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KKGR0E1X2J8YA1DX900C9W7D</t>
         </is>
       </c>
     </row>

--- a/site/ServiceNow-Entra-ID-Okta-Integration-Guide/headings.xlsx
+++ b/site/ServiceNow-Entra-ID-Okta-Integration-Guide/headings.xlsx
@@ -925,7 +925,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Notifications Settings</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">

--- a/site/ServiceNow-Entra-ID-Okta-Integration-Guide/headings.xlsx
+++ b/site/ServiceNow-Entra-ID-Okta-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -705,7 +705,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unique Identity</t>
+          <t>Password Policy</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,19 +715,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
+          <t>h_01KJYCFGY00P3DCSPHSZ72MP8V</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY00P3DCSPHSZ72MP8V</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unique Identity Settings</t>
+          <t>Password Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,19 +737,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KKBN5W79VGJ9JG0FGSVGT1A7</t>
+          <t>h_01KKBN5W79A97TWK76DQW39BVF</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KKBN5W79VGJ9JG0FGSVGT1A7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KKBN5W79A97TWK76DQW39BVF</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Password Policy</t>
+          <t>Unique Identity</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,19 +759,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KJYCFGY00P3DCSPHSZ72MP8V</t>
+          <t>h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY00P3DCSPHSZ72MP8V</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Password Settings</t>
+          <t>Unique Identity Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KKBN5W79A97TWK76DQW39BVF</t>
+          <t>h_01KKBN5W79VGJ9JG0FGSVGT1A7</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KKBN5W79A97TWK76DQW39BVF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KKBN5W79VGJ9JG0FGSVGT1A7</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Onboarding Notification Settings</t>
+          <t>Successful Integration Notification Settings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,19 +979,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KJYCFGY0AG0E1C2SFT0ZEDDK</t>
+          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY0AG0E1C2SFT0ZEDDK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Offboarding Notification Settings</t>
+          <t>Failed Integration Notification Settings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1001,85 +1001,85 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KJYCFGY02MABCNX128SC7YSA</t>
+          <t>h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KJYCFGY02MABCNX128SC7YSA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Skipped Execution Notification Settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>h_01KKZY9Y2XD0A7KBJZ4HXYZ17V</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KKZY9Y2XD0A7KBJZ4HXYZ17V</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
+          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Group Rules</t>
+          <t>Log Insight Settings</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>01JVC7QW1983644JGH2WGK8FWX</t>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01JVC7QW1983644JGH2WGK8FWX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1089,54 +1089,98 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
+          <t>h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Group Rules</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>01JVC7QW1983644JGH2WGK8FWX</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01JVC7QW1983644JGH2WGK8FWX</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/ServiceNow-Entra-ID-Okta-Integration-Guide/headings.xlsx
+++ b/site/ServiceNow-Entra-ID-Okta-Integration-Guide/headings.xlsx
@@ -1023,12 +1023,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KKZY9Y2XD0A7KBJZ4HXYZ17V</t>
+          <t>h_01KKZYQ9RKF787CKNBVZR47SHJ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KKZY9Y2XD0A7KBJZ4HXYZ17V</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ServiceNow-Entra-ID-Okta-Integration-Guide/#h_01KKZYQ9RKF787CKNBVZR47SHJ</t>
         </is>
       </c>
     </row>
